--- a/backtesting_trading_journal_pro_fixed.xlsx
+++ b/backtesting_trading_journal_pro_fixed.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Visso\Desktop\journal_trading\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\journal_trading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E957FFA-3844-413F-BAB6-84AED257EC1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Trading Journal" sheetId="1" r:id="rId1"/>
     <sheet name="Statistiques" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
   <si>
     <t>Date</t>
   </si>
@@ -69,9 +68,6 @@
   </si>
   <si>
     <t>Capital Après ($)</t>
-  </si>
-  <si>
-    <t>Lien Screenshot</t>
   </si>
   <si>
     <t>Notes</t>
@@ -169,11 +165,26 @@
   <si>
     <t>Daily , H4 , H1, M15 ,M5</t>
   </si>
+  <si>
+    <t>Name Screenshot</t>
+  </si>
+  <si>
+    <t>BTCUSD_2026-03-15 042122</t>
+  </si>
+  <si>
+    <t>CADJPY_2026-03-17 042232</t>
+  </si>
+  <si>
+    <t>EURJPY_2026-03-13 041840</t>
+  </si>
+  <si>
+    <t>US30_2026-03-18 041657</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
@@ -542,9 +553,6 @@
     <xf numFmtId="14" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -557,33 +565,14 @@
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="14">
     <dxf>
       <font>
         <b/>
@@ -609,26 +598,6 @@
     <dxf>
       <font>
         <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <i val="0"/>
         <color theme="0"/>
       </font>
@@ -645,16 +614,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -830,23 +789,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="JournalTrading" displayName="JournalTrading" ref="A1:N200" totalsRowShown="0">
-  <autoFilter ref="A1:N200" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="JournalTrading" displayName="JournalTrading" ref="A1:N200" totalsRowShown="0">
+  <autoFilter ref="A1:N200"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Date"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Paire"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Timeframe"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Stratégie / Setup"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Type (Buy/Sell)"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Risk Amount"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Risk/Reward"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Résultat (Win/Loss)"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Pips"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Capital Avant ($)"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Capital Après ($)"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Lien Screenshot"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Notes"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="État Émotionnel"/>
+    <tableColumn id="1" name="Date"/>
+    <tableColumn id="2" name="Paire"/>
+    <tableColumn id="3" name="Timeframe"/>
+    <tableColumn id="4" name="Stratégie / Setup"/>
+    <tableColumn id="5" name="Type (Buy/Sell)"/>
+    <tableColumn id="6" name="Risk Amount"/>
+    <tableColumn id="7" name="Risk/Reward"/>
+    <tableColumn id="8" name="Résultat (Win/Loss)"/>
+    <tableColumn id="9" name="Pips"/>
+    <tableColumn id="10" name="Capital Avant ($)"/>
+    <tableColumn id="11" name="Capital Après ($)"/>
+    <tableColumn id="12" name="Name Screenshot"/>
+    <tableColumn id="13" name="Notes"/>
+    <tableColumn id="14" name="État Émotionnel"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1030,7 +989,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N201"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="23.25" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1082,39 +1041,39 @@
         <v>10</v>
       </c>
       <c r="L1" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>18</v>
       </c>
       <c r="F2" s="9">
         <v>2</v>
       </c>
       <c r="G2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="12" t="s">
         <v>19</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>20</v>
       </c>
       <c r="I2" s="9">
         <v>149</v>
@@ -1126,36 +1085,38 @@
         <f t="shared" ref="K2:K33" si="0">IF(H2="","",IF(H2="Win",J2+(F2*VALUE(RIGHT(G2,1))),IF(H2="Loss",J2-F2,IF(H2="En cours","En cours",J2))))</f>
         <v>26</v>
       </c>
-      <c r="L2" s="15"/>
+      <c r="L2" s="15" t="s">
+        <v>46</v>
+      </c>
       <c r="M2" s="16"/>
       <c r="N2" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="18" t="s">
         <v>23</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>24</v>
       </c>
       <c r="F3" s="9">
         <v>6</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" s="9">
         <v>258</v>
@@ -1167,10 +1128,12 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="L3" s="15"/>
+      <c r="L3" s="15" t="s">
+        <v>44</v>
+      </c>
       <c r="M3" s="16"/>
       <c r="N3" s="17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -1178,25 +1141,25 @@
         <v>46097</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="20" t="s">
-        <v>17</v>
-      </c>
       <c r="E4" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" s="20">
         <v>4.97</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="44" t="s">
-        <v>41</v>
+        <v>26</v>
+      </c>
+      <c r="H4" s="43" t="s">
+        <v>40</v>
       </c>
       <c r="I4" s="20">
         <v>88</v>
@@ -1205,47 +1168,53 @@
         <v>54</v>
       </c>
       <c r="K4" s="24">
-        <f t="shared" si="0"/>
+        <f>IF(H4="","",IF(H4="Win",J4+(F4*VALUE(RIGHT(G4,1))),IF(H4="Loss",J4-F4,IF(H4="En cours","En cours",J4))))</f>
         <v>49.03</v>
       </c>
-      <c r="L4" s="25"/>
+      <c r="L4" s="25" t="s">
+        <v>45</v>
+      </c>
       <c r="M4" s="26"/>
       <c r="N4" s="27"/>
     </row>
     <row r="5" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41">
+      <c r="A5" s="40">
         <v>46097</v>
       </c>
       <c r="B5" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="28" t="s">
-        <v>43</v>
-      </c>
       <c r="D5" s="28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F5" s="28">
         <v>16.84</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="41">
         <v>5.486111111111111E-2</v>
       </c>
-      <c r="H5" s="43" t="s">
-        <v>28</v>
+      <c r="H5" s="42" t="s">
+        <v>27</v>
       </c>
       <c r="I5" s="28">
         <v>377749</v>
       </c>
-      <c r="J5" s="28"/>
+      <c r="J5" s="28">
+        <v>49.03</v>
+      </c>
       <c r="K5" s="29" t="str">
         <f t="shared" si="0"/>
         <v>En cours</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="28" t="s">
+        <v>47</v>
+      </c>
       <c r="M5" s="28"/>
       <c r="N5" s="28"/>
     </row>
@@ -4975,31 +4944,31 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="H4">
-    <cfRule type="cellIs" dxfId="18" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="4" operator="equal">
       <formula>"En cours"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="5" operator="equal">
       <formula>"Win"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="6" operator="equal">
       <formula>"Lost"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2">
-    <cfRule type="cellIs" dxfId="15" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
       <formula>"Win"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
       <formula>"Lost"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"Win"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:F2">
-    <cfRule type="cellIs" dxfId="12" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
       <formula>"Sell"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="11" operator="equal">
@@ -5007,12 +4976,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:F3">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="12" operator="equal">
       <formula>"Sell"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:F1048576">
-    <cfRule type="cellIs" dxfId="10" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="13" operator="equal">
       <formula>"Buy"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5020,55 +4989,55 @@
     <cfRule type="cellIs" dxfId="4" priority="14" operator="equal">
       <formula>"Lost"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="15" operator="equal">
       <formula>"Win"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"En cours"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Loss"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H5">
-    <cfRule type="cellIs" dxfId="9" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="16" operator="equal">
       <formula>"Lost"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1201" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E1:E1201">
       <formula1>"Buy,Sell"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A1201" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A1:A1201">
       <formula1>43831</formula1>
       <formula2>49674</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H202:H1201" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1 H202:H1201">
       <formula1>"Win,Lost,En cours"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1201" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1201">
       <formula1>"Heltrading ( DKH )"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B3 B5:B1201" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B1:B3 B5:B1201">
       <formula1>"BTCUSD,CADJPY,CHFJPY,EURJPY,EURUSD,GBPUSD,NZDUSD,US100,US30,USDJPY,XAUUSD,EURNZD,GBPJPY"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4">
       <formula1>"BTCUSD,CADJPY,CHFJPY,EURJPY,EURUSD,GBPUSD,GBPNZD,NZDUSD,US100,US30,USDJPY,XAUUSD,EURNZD,GBPJPY,"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="État Émotionnel" prompt="Sélectionnez votre état émotionnel" sqref="N2:N201" xr:uid="{00000000-0002-0000-0000-000008000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="État Émotionnel" prompt="Sélectionnez votre état émotionnel" sqref="N2:N201">
       <formula1>"Calme,Confiant,Hésitant,Stressé,Euphorique,Neutre,Fatigué,Revanche"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H201" xr:uid="{00000000-0002-0000-0000-000009000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H201">
       <formula1>"Win,Loss,En cours"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{C284FB54-E6E1-4558-B7D3-088DBDEAB886}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576">
       <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
         <mc:Choice Requires="x12ac">
           <x12ac:list>"Daily , H4 , H1, M15 ,M5"," Daily , H4 , H1, M15 ,M5 ,M1"," Daily , H4 , H1, M15 "</x12ac:list>
@@ -5078,7 +5047,7 @@
         </mc:Fallback>
       </mc:AlternateContent>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576" xr:uid="{20F5209D-0D47-43FA-9F63-A5DE3FBD29F7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1:G1048576">
       <formula1>"1:2 ,1:3 ,1:4 ,1:5,1:6 ,1:7 ,1:8 ,1:9,1:10,1:19"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5091,7 +5060,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5100,14 +5069,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="40"/>
+      <c r="A1" s="44" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="44"/>
     </row>
     <row r="2" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="33">
         <f>COUNTA('Trading Journal'!A2:A201)</f>
@@ -5116,7 +5085,7 @@
     </row>
     <row r="3" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B3" s="34">
         <f>COUNTIF('Trading Journal'!H2:H201,"Win")</f>
@@ -5125,7 +5094,7 @@
     </row>
     <row r="4" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B4" s="35">
         <f>COUNTIF('Trading Journal'!H2:H201,"Loss")</f>
@@ -5134,7 +5103,7 @@
     </row>
     <row r="5" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="36">
         <f>COUNTIF('Trading Journal'!H2:H201,"En cours")</f>
@@ -5143,7 +5112,7 @@
     </row>
     <row r="6" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="33" t="str">
         <f>IF(B3+B4=0,"",ROUND(B3/(B3+B4)*100,1)&amp;"%")</f>
@@ -5152,7 +5121,7 @@
     </row>
     <row r="7" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="37">
         <f>'Trading Journal'!J2</f>
@@ -5161,7 +5130,7 @@
     </row>
     <row r="8" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B8" s="38" t="str">
         <f>IFERROR(LOOKUP(2,1/('Trading Journal'!K2:K201&lt;&gt;""),'Trading Journal'!K2:K201),"—")</f>
@@ -5170,7 +5139,7 @@
     </row>
     <row r="9" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" s="38">
         <f>IFERROR(SUMIF('Trading Journal'!H2:H201,"Win",'Trading Journal'!K2:K201)-SUMIF('Trading Journal'!H2:H201,"Win",'Trading Journal'!J2:J201)-(SUMIF('Trading Journal'!H2:H201,"Loss",'Trading Journal'!F2:F201)),0)</f>
@@ -5179,7 +5148,7 @@
     </row>
     <row r="10" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="37">
         <f>IFERROR(AVERAGEIF('Trading Journal'!H2:H201,"&lt;&gt;",'Trading Journal'!F2:F201),"—")</f>
@@ -5188,7 +5157,7 @@
     </row>
     <row r="11" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="34">
         <f>IFERROR(SUMIF('Trading Journal'!H2:H201,"Win",'Trading Journal'!I2:I201),0)</f>
@@ -5197,7 +5166,7 @@
     </row>
     <row r="12" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="34">
         <f>IFERROR(MAX(IF('Trading Journal'!H2:H201="Win",VALUE(RIGHT('Trading Journal'!G2:G201,1)))),"—")</f>
